--- a/pregenerated_results/ate_summary_survey.xlsx
+++ b/pregenerated_results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3982233096578142</v>
+        <v>0.3985398745276547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03926983810596112</v>
+        <v>0.03933933271771812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3212558412914118</v>
+        <v>0.3214361992250889</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4751907780242166</v>
+        <v>0.4756435498302204</v>
       </c>
       <c r="G2" t="n">
-        <v>3.645104327879733e-24</v>
+        <v>4.032349524444037e-24</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4740212656916218</v>
+        <v>0.4677085962881639</v>
       </c>
       <c r="I2" t="n">
-        <v>11.8520500782549</v>
+        <v>11.70361347220282</v>
       </c>
       <c r="J2" t="n">
-        <v>3.783304057116402</v>
+        <v>3.77881082367578</v>
       </c>
       <c r="K2" t="n">
-        <v>3.382418162625982</v>
+        <v>3.382890406330613</v>
       </c>
       <c r="L2" t="n">
         <v>7220</v>
       </c>
       <c r="M2" t="n">
-        <v>7094.386718944053</v>
+        <v>7095.308361203054</v>
       </c>
       <c r="N2" t="n">
-        <v>1.09353129836392e-23</v>
+        <v>1.209704857333211e-23</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0405928052277169</v>
+        <v>-0.04071597969725242</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,37 +591,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04219295914182773</v>
+        <v>0.04219485817141799</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1232894855468693</v>
+        <v>-0.1234163820460073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04210387509143548</v>
+        <v>0.04198442265150244</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3360117637295972</v>
+        <v>0.3345692469681957</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06073443341649937</v>
+        <v>-0.06413795733398037</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.775147039486122</v>
+        <v>-1.874509212109839</v>
       </c>
       <c r="J3" t="n">
-        <v>3.134720965027061</v>
+        <v>3.131806206400518</v>
       </c>
       <c r="K3" t="n">
-        <v>3.191372519831829</v>
+        <v>3.191633673629502</v>
       </c>
       <c r="L3" t="n">
         <v>7220</v>
       </c>
       <c r="M3" t="n">
-        <v>7094.386718944053</v>
+        <v>7093.805668076424</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3360117637295972</v>
+        <v>0.3345692469681957</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2300267851900341</v>
+        <v>0.2303472064753822</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,37 +648,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0427568726402331</v>
+        <v>0.04274619914367982</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1462248547236112</v>
+        <v>0.1465661956777928</v>
       </c>
       <c r="F4" t="n">
-        <v>0.313828715656457</v>
+        <v>0.3141282172729715</v>
       </c>
       <c r="G4" t="n">
-        <v>7.453607464503609e-08</v>
+        <v>7.096210791271912e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2684816016281894</v>
+        <v>0.2528818070312245</v>
       </c>
       <c r="I4" t="n">
-        <v>9.109177240226145</v>
+        <v>8.576871305907101</v>
       </c>
       <c r="J4" t="n">
-        <v>3.052316367566833</v>
+        <v>3.038978091517199</v>
       </c>
       <c r="K4" t="n">
-        <v>2.797488208390147</v>
+        <v>2.798918457463292</v>
       </c>
       <c r="L4" t="n">
         <v>7220</v>
       </c>
       <c r="M4" t="n">
-        <v>7094.386718944053</v>
+        <v>7093.528441237814</v>
       </c>
       <c r="N4" t="n">
-        <v>1.118041119675541e-07</v>
+        <v>1.064431618690787e-07</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
